--- a/Soluciones en Excel/L-VaR de futuros.xlsx
+++ b/Soluciones en Excel/L-VaR de futuros.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charly Oceguera\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/106876cc2438bd37/Desktop/TRABAJO/UNI/8VO SEMESTRE/ADMINISTRACION_RIESGOS/Soluciones en Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB457F6-E2CD-4EB1-A287-1187F93A0EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7FB457F6-E2CD-4EB1-A287-1187F93A0EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86C35DCB-FC1B-4DC5-B1B5-6E04E888B07F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nat Gas Henry Hub" sheetId="2" r:id="rId1"/>
@@ -329,7 +329,7 @@
             <c:numRef>
               <c:f>'Volatilidad y liquidez-spread'!$A$4:$A$234</c:f>
               <c:numCache>
-                <c:formatCode>mm/dd/\y\y</c:formatCode>
+                <c:formatCode>mm/dd/yy</c:formatCode>
                 <c:ptCount val="231"/>
                 <c:pt idx="0">
                   <c:v>46050</c:v>
@@ -1782,7 +1782,7 @@
             <c:numRef>
               <c:f>'Volatilidad y liquidez-spread'!$A$4:$A$234</c:f>
               <c:numCache>
-                <c:formatCode>mm/dd/\y\y</c:formatCode>
+                <c:formatCode>mm/dd/yy</c:formatCode>
                 <c:ptCount val="231"/>
                 <c:pt idx="0">
                   <c:v>46050</c:v>
@@ -3209,7 +3209,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="mm/dd/\y\y" sourceLinked="1"/>
+        <c:numFmt formatCode="mm/dd/yy" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3357,11 +3357,12 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="mm/dd/\y\y" sourceLinked="1"/>
+        <c:numFmt formatCode="mm/dd/yy" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1069676416"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
@@ -4405,26 +4406,27 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:O255"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="4" width="8.26953125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="7" width="4.81640625" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="7" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -4456,7 +4458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>46050</v>
       </c>
@@ -4496,7 +4498,7 @@
         <v>9.7777784158101094E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46049</v>
       </c>
@@ -4536,7 +4538,7 @@
         <v>7.6721116861763698E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>46048</v>
       </c>
@@ -4569,7 +4571,7 @@
         <v>3.6335323124837247E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>46045</v>
       </c>
@@ -4605,7 +4607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>46044</v>
       </c>
@@ -4638,7 +4640,7 @@
         <v>1.2958963282937344E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>46043</v>
       </c>
@@ -4678,7 +4680,7 @@
         <v>1.3826899322300525E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>46042</v>
       </c>
@@ -4711,7 +4713,7 @@
         <v>2.0252375759464075E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>46038</v>
       </c>
@@ -4751,7 +4753,7 @@
         <v>2.3263478740408408</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>46037</v>
       </c>
@@ -4791,7 +4793,7 @@
         <v>1.9599639845400536</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>46036</v>
       </c>
@@ -4831,7 +4833,7 @@
         <v>1.6448536269514715</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>46035</v>
       </c>
@@ -4864,7 +4866,7 @@
         <v>2.473436683504622E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>46034</v>
       </c>
@@ -4907,7 +4909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>46031</v>
       </c>
@@ -4943,7 +4945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>46030</v>
       </c>
@@ -4979,7 +4981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>46029</v>
       </c>
@@ -5015,7 +5017,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>46028</v>
       </c>
@@ -5051,7 +5053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>46027</v>
       </c>
@@ -5084,7 +5086,7 @@
         <v>9.7188476223533573E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46024</v>
       </c>
@@ -5117,7 +5119,7 @@
         <v>1.2349691257718641E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>46022</v>
       </c>
@@ -5150,7 +5152,7 @@
         <v>1.5878056525881177E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46021</v>
       </c>
@@ -5183,7 +5185,7 @@
         <v>2.8127313101406294E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>46020</v>
       </c>
@@ -5216,7 +5218,7 @@
         <v>1.4705882352941284E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46017</v>
       </c>
@@ -5249,7 +5251,7 @@
         <v>2.1525074421799729E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>46015</v>
       </c>
@@ -5282,7 +5284,7 @@
         <v>2.5041341837939966E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>46014</v>
       </c>
@@ -5315,7 +5317,7 @@
         <v>4.9841413683734126E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>46013</v>
       </c>
@@ -5348,7 +5350,7 @@
         <v>4.5101478326233513E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>46010</v>
       </c>
@@ -5381,7 +5383,7 @@
         <v>1.0978043912175658E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>46009</v>
       </c>
@@ -5414,7 +5416,7 @@
         <v>1.376848546659863E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>46008</v>
       </c>
@@ -5447,7 +5449,7 @@
         <v>2.6812918951856753E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>46007</v>
       </c>
@@ -5480,7 +5482,7 @@
         <v>1.1976047904191656E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>46006</v>
       </c>
@@ -5513,7 +5515,7 @@
         <v>8.1855388813097778E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>46003</v>
       </c>
@@ -5546,7 +5548,7 @@
         <v>2.4727272727272803E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>46002</v>
       </c>
@@ -5579,7 +5581,7 @@
         <v>4.9557522123893577E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>46001</v>
       </c>
@@ -5612,7 +5614,7 @@
         <v>6.2723045311992897E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>46000</v>
       </c>
@@ -5645,7 +5647,7 @@
         <v>3.7154409354167766E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>45999</v>
       </c>
@@ -5678,7 +5680,7 @@
         <v>4.3152162745299302E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>45996</v>
       </c>
@@ -5711,7 +5713,7 @@
         <v>1.0530274539300499E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>45995</v>
       </c>
@@ -5744,7 +5746,7 @@
         <v>5.1352952794785313E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>45994</v>
       </c>
@@ -5777,7 +5779,7 @@
         <v>4.1878552198625577E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>45993</v>
       </c>
@@ -5810,7 +5812,7 @@
         <v>4.9771878888428094E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>45992</v>
       </c>
@@ -5843,7 +5845,7 @@
         <v>7.9583715947351696E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>45989</v>
       </c>
@@ -5876,7 +5878,7 @@
         <v>1.1140911904270556E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45987</v>
       </c>
@@ -5909,7 +5911,7 @@
         <v>2.8153762858689553E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45986</v>
       </c>
@@ -5942,7 +5944,7 @@
         <v>4.4603033006243471E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>45985</v>
       </c>
@@ -5975,7 +5977,7 @@
         <v>6.2412568600021343E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>45982</v>
       </c>
@@ -6008,7 +6010,7 @@
         <v>1.4425116673737907E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>45981</v>
       </c>
@@ -6041,7 +6043,7 @@
         <v>9.3916755602987383E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>45980</v>
       </c>
@@ -6074,7 +6076,7 @@
         <v>1.0492078480746814E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>45979</v>
       </c>
@@ -6103,7 +6105,7 @@
         <v>1.4827736589620694E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>45978</v>
       </c>
@@ -6136,7 +6138,7 @@
         <v>8.0989383824012079E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>45975</v>
       </c>
@@ -6169,7 +6171,7 @@
         <v>1.8632225280542043E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>45974</v>
       </c>
@@ -6202,7 +6204,7 @@
         <v>5.2153958485449785E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>45973</v>
       </c>
@@ -6235,7 +6237,7 @@
         <v>5.6884019804066448E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>45972</v>
       </c>
@@ -6268,7 +6270,7 @@
         <v>2.9642176582680992E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>45971</v>
       </c>
@@ -6301,7 +6303,7 @@
         <v>1.5486966953866229E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>45968</v>
       </c>
@@ -6334,7 +6336,7 @@
         <v>2.0776380535811864E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>45967</v>
       </c>
@@ -6367,7 +6369,7 @@
         <v>2.6701685270299823E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>45966</v>
       </c>
@@ -6400,7 +6402,7 @@
         <v>2.4246468690913132E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>45965</v>
       </c>
@@ -6433,7 +6435,7 @@
         <v>8.5516938932133982E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>45964</v>
       </c>
@@ -6466,7 +6468,7 @@
         <v>1.2242626599888642E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>45961</v>
       </c>
@@ -6499,7 +6501,7 @@
         <v>1.1902037079423118E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>45960</v>
       </c>
@@ -6532,7 +6534,7 @@
         <v>6.9767441860465679E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>45959</v>
       </c>
@@ -6565,7 +6567,7 @@
         <v>-2.9944602485398707E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>45958</v>
       </c>
@@ -6598,7 +6600,7 @@
         <v>2.4615384615384638E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>45957</v>
       </c>
@@ -6631,7 +6633,7 @@
         <v>1.1713030746705721E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>45954</v>
       </c>
@@ -6664,7 +6666,7 @@
         <v>2.0038881411694253E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>45953</v>
       </c>
@@ -6697,7 +6699,7 @@
         <v>6.9834522544406051E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>45952</v>
       </c>
@@ -6730,7 +6732,7 @@
         <v>6.6734368199623181E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>45951</v>
       </c>
@@ -6763,7 +6765,7 @@
         <v>3.7243947858472716E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>45950</v>
       </c>
@@ -6796,7 +6798,7 @@
         <v>1.4975774482454898E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>45947</v>
       </c>
@@ -6829,7 +6831,7 @@
         <v>3.6623938738137764E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>45946</v>
       </c>
@@ -6862,7 +6864,7 @@
         <v>3.7600410186293355E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>45945</v>
       </c>
@@ -6895,7 +6897,7 @@
         <v>2.3090879102754796E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>45944</v>
       </c>
@@ -6928,7 +6930,7 @@
         <v>3.9643211100099142E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>45943</v>
       </c>
@@ -6961,7 +6963,7 @@
         <v>4.837929366231293E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>45940</v>
       </c>
@@ -6994,7 +6996,7 @@
         <v>1.3038638893305749E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>45939</v>
       </c>
@@ -7027,7 +7029,7 @@
         <v>5.5572707625811176E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>45938</v>
       </c>
@@ -7060,7 +7062,7 @@
         <v>3.5938903863432193E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>45937</v>
       </c>
@@ -7093,7 +7095,7 @@
         <v>3.6905606813342515E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>45936</v>
       </c>
@@ -7126,7 +7128,7 @@
         <v>9.1216713255848573E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>45933</v>
       </c>
@@ -7159,7 +7161,7 @@
         <v>1.4650919419943302E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>45932</v>
       </c>
@@ -7192,7 +7194,7 @@
         <v>4.1079812206573458E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>45931</v>
       </c>
@@ -7225,7 +7227,7 @@
         <v>7.5406032482598032E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>45930</v>
       </c>
@@ -7258,7 +7260,7 @@
         <v>1.800720288115181E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>45929</v>
       </c>
@@ -7291,7 +7293,7 @@
         <v>3.9712845578127086E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>45926</v>
       </c>
@@ -7324,7 +7326,7 @@
         <v>8.4838963079340562E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>45925</v>
       </c>
@@ -7357,7 +7359,7 @@
         <v>2.4760136180749016E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>45924</v>
       </c>
@@ -7390,7 +7392,7 @@
         <v>4.1276393078267491E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>45923</v>
       </c>
@@ -7423,7 +7425,7 @@
         <v>3.4922297887197127E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>45922</v>
       </c>
@@ -7456,7 +7458,7 @@
         <v>6.0530532312623635E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>45919</v>
       </c>
@@ -7489,7 +7491,7 @@
         <v>2.0547945205480231E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>45918</v>
       </c>
@@ -7522,7 +7524,7 @@
         <v>5.4384772263766194E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>45917</v>
       </c>
@@ -7555,7 +7557,7 @@
         <v>2.5990903183885665E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>45916</v>
       </c>
@@ -7588,7 +7590,7 @@
         <v>1.9249278152070027E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>45915</v>
       </c>
@@ -7621,7 +7623,7 @@
         <v>5.2596975673898797E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>45912</v>
       </c>
@@ -7654,7 +7656,7 @@
         <v>9.4754653130287737E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>45911</v>
       </c>
@@ -7687,7 +7689,7 @@
         <v>1.0275732145914264E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>45910</v>
       </c>
@@ -7720,7 +7722,7 @@
         <v>4.2883061190829297E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>45909</v>
       </c>
@@ -7753,7 +7755,7 @@
         <v>8.3574413371906939E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>45908</v>
       </c>
@@ -7786,7 +7788,7 @@
         <v>3.8747174685179234E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>45905</v>
       </c>
@@ -7819,7 +7821,7 @@
         <v>1.1530225662988024E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>45904</v>
       </c>
@@ -7852,7 +7854,7 @@
         <v>2.2738346597367788E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>45903</v>
       </c>
@@ -7885,7 +7887,7 @@
         <v>4.558775643112925E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>45902</v>
       </c>
@@ -7918,7 +7920,7 @@
         <v>7.6858813700919409E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>45898</v>
       </c>
@@ -7951,7 +7953,7 @@
         <v>1.0968921389396683E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>45897</v>
       </c>
@@ -7984,7 +7986,7 @@
         <v>9.0649655867047624E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>45896</v>
       </c>
@@ -8017,7 +8019,7 @@
         <v>3.8240917782027188E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>45895</v>
       </c>
@@ -8050,7 +8052,7 @@
         <v>5.669737774627928E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>45894</v>
       </c>
@@ -8083,7 +8085,7 @@
         <v>6.387508871540026E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>45891</v>
       </c>
@@ -8116,7 +8118,7 @@
         <v>4.6453457209220464E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>45890</v>
       </c>
@@ -8149,7 +8151,7 @@
         <v>6.4056939501778622E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>45889</v>
       </c>
@@ -8182,7 +8184,7 @@
         <v>6.5241029358462464E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>45888</v>
       </c>
@@ -8215,7 +8217,7 @@
         <v>6.1605363290450823E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>45887</v>
       </c>
@@ -8248,7 +8250,7 @@
         <v>6.1919504643962141E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>45884</v>
       </c>
@@ -8281,7 +8283,7 @@
         <v>1.025641025641019E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>45883</v>
       </c>
@@ -8314,7 +8316,7 @@
         <v>5.6239015817223246E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>45882</v>
       </c>
@@ -8347,7 +8349,7 @@
         <v>3.5460992907802233E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>45881</v>
       </c>
@@ -8380,7 +8382,7 @@
         <v>6.1030335666845828E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>45880</v>
       </c>
@@ -8413,7 +8415,7 @@
         <v>1.6764459346185728E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>45877</v>
       </c>
@@ -8446,7 +8448,7 @@
         <v>2.3383998663770414E-3</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>45876</v>
       </c>
@@ -8479,7 +8481,7 @@
         <v>5.516793769268182E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>45875</v>
       </c>
@@ -8512,7 +8514,7 @@
         <v>6.1538461538461955E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>45874</v>
       </c>
@@ -8545,7 +8547,7 @@
         <v>4.654255319149014E-3</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>45873</v>
       </c>
@@ -8578,7 +8580,7 @@
         <v>5.761735299101815E-3</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>45870</v>
       </c>
@@ -8611,7 +8613,7 @@
         <v>1.4551333872271744E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>45869</v>
       </c>
@@ -8644,7 +8646,7 @@
         <v>4.8348106365832975E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>45868</v>
       </c>
@@ -8677,7 +8679,7 @@
         <v>8.268562923763819E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>45867</v>
       </c>
@@ -8710,7 +8712,7 @@
         <v>4.7430830039526094E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>45866</v>
       </c>
@@ -8743,7 +8745,7 @@
         <v>4.5117628101836258E-3</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>45863</v>
       </c>
@@ -8776,7 +8778,7 @@
         <v>9.1932160405769261E-3</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>45862</v>
       </c>
@@ -8809,7 +8811,7 @@
         <v>9.8303472332329587E-3</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>45861</v>
       </c>
@@ -8842,7 +8844,7 @@
         <v>1.0262989095574096E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>45860</v>
       </c>
@@ -8875,7 +8877,7 @@
         <v>1.4313994213491747E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>45859</v>
       </c>
@@ -8908,7 +8910,7 @@
         <v>1.2548550941141266E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>45856</v>
       </c>
@@ -8941,7 +8943,7 @@
         <v>2.930914166085136E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>45855</v>
       </c>
@@ -8974,7 +8976,7 @@
         <v>1.6830294530154291E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>45854</v>
       </c>
@@ -9007,7 +9009,7 @@
         <v>8.3449235048678183E-3</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>45853</v>
       </c>
@@ -9040,7 +9042,7 @@
         <v>1.067715650463608E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>45852</v>
       </c>
@@ -9073,7 +9075,7 @@
         <v>2.0011435105774682E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>45849</v>
       </c>
@@ -9106,7 +9108,7 @@
         <v>1.5526585615936703E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>45848</v>
       </c>
@@ -9139,7 +9141,7 @@
         <v>3.7780752640190325E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>45847</v>
       </c>
@@ -9172,7 +9174,7 @@
         <v>3.014457090126111E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>45846</v>
       </c>
@@ -9205,7 +9207,7 @@
         <v>3.2615026208503234E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>45845</v>
       </c>
@@ -9238,7 +9240,7 @@
         <v>7.5757575757575179E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>45841</v>
       </c>
@@ -9271,7 +9273,7 @@
         <v>7.8866656930041464E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>45840</v>
       </c>
@@ -9304,7 +9306,7 @@
         <v>2.5604551920341351E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>45839</v>
       </c>
@@ -9337,7 +9339,7 @@
         <v>1.305293691080504E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>45838</v>
       </c>
@@ -9370,7 +9372,7 @@
         <v>1.1524056467876702E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>45835</v>
       </c>
@@ -9403,7 +9405,7 @@
         <v>2.0618556701030917E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>45834</v>
       </c>
@@ -9436,7 +9438,7 @@
         <v>1.2918732161634415E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>45833</v>
       </c>
@@ -9469,7 +9471,7 @@
         <v>2.9489826010025912E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>45832</v>
       </c>
@@ -9502,7 +9504,7 @@
         <v>3.0946687297791872E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>45831</v>
       </c>
@@ -9535,7 +9537,7 @@
         <v>1.0541965130422949E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>45828</v>
       </c>
@@ -9568,7 +9570,7 @@
         <v>6.9471246622924716E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>45826</v>
       </c>
@@ -9601,7 +9603,7 @@
         <v>5.2757191307624433E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>45825</v>
       </c>
@@ -9634,7 +9636,7 @@
         <v>5.4368932038835862E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>45824</v>
       </c>
@@ -9667,7 +9669,7 @@
         <v>2.4048096192384495E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>45821</v>
       </c>
@@ -9700,7 +9702,7 @@
         <v>1.111111111111112E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>45820</v>
       </c>
@@ -9733,7 +9735,7 @@
         <v>4.8070125830623226E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>45819</v>
       </c>
@@ -9766,7 +9768,7 @@
         <v>3.9806653397782867E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>45818</v>
       </c>
@@ -9799,7 +9801,7 @@
         <v>3.6926572929982513E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>45817</v>
       </c>
@@ -9832,7 +9834,7 @@
         <v>6.9396252602360459E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>45814</v>
       </c>
@@ -9865,7 +9867,7 @@
         <v>6.3224446786090682E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>45813</v>
       </c>
@@ -9898,7 +9900,7 @@
         <v>4.9207217058501347E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>45812</v>
       </c>
@@ -9931,7 +9933,7 @@
         <v>2.6990553306342202E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>45811</v>
       </c>
@@ -9964,7 +9966,7 @@
         <v>2.4151348450288201E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>45810</v>
       </c>
@@ -9997,7 +9999,7 @@
         <v>1.8684105164820811E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>45807</v>
       </c>
@@ -10030,7 +10032,7 @@
         <v>1.5037593984962419E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>45806</v>
       </c>
@@ -10063,7 +10065,7 @@
         <v>6.2199604184337695E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>45805</v>
       </c>
@@ -10096,7 +10098,7 @@
         <v>4.8097326354506571E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>45804</v>
       </c>
@@ -10129,7 +10131,7 @@
         <v>3.1957390146471402E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>45800</v>
       </c>
@@ -10162,7 +10164,7 @@
         <v>9.4530722484807948E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>45799</v>
       </c>
@@ -10195,7 +10197,7 @@
         <v>8.152173913043426E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>45798</v>
       </c>
@@ -10228,7 +10230,7 @@
         <v>2.5180819716046042E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>45797</v>
       </c>
@@ -10261,7 +10263,7 @@
         <v>1.1235955056179726E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>45796</v>
       </c>
@@ -10294,7 +10296,7 @@
         <v>2.5974025974025934E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>45793</v>
       </c>
@@ -10327,7 +10329,7 @@
         <v>1.594379137954335E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
         <v>45792</v>
       </c>
@@ -10360,7 +10362,7 @@
         <v>1.2854847348687746E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>45791</v>
       </c>
@@ -10393,7 +10395,7 @@
         <v>1.0010537407797631E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3">
         <v>45790</v>
       </c>
@@ -10426,7 +10428,7 @@
         <v>8.866371120962559E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>45789</v>
       </c>
@@ -10459,7 +10461,7 @@
         <v>4.7422937726195255E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>45786</v>
       </c>
@@ -10492,7 +10494,7 @@
         <v>2.233402871517982E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>45785</v>
       </c>
@@ -10525,7 +10527,7 @@
         <v>2.8852291586876033E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>45784</v>
       </c>
@@ -10558,7 +10560,7 @@
         <v>1.3716027432054819E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>45783</v>
       </c>
@@ -10591,7 +10593,7 @@
         <v>1.2699235454192026E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>45782</v>
       </c>
@@ -10624,7 +10626,7 @@
         <v>5.3497425593369355E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>45779</v>
       </c>
@@ -10657,7 +10659,7 @@
         <v>2.4996843832849329E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>45778</v>
       </c>
@@ -10690,7 +10692,7 @@
         <v>1.6788807461692132E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>45777</v>
       </c>
@@ -10723,7 +10725,7 @@
         <v>6.8352699931647064E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>45776</v>
       </c>
@@ -10756,7 +10758,7 @@
         <v>2.3650944678537501E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>45775</v>
       </c>
@@ -10789,7 +10791,7 @@
         <v>2.4526198439241906E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>45772</v>
       </c>
@@ -10822,7 +10824,7 @@
         <v>4.2992261392949267E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>45771</v>
       </c>
@@ -10855,7 +10857,7 @@
         <v>1.7094017094017186E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>45770</v>
       </c>
@@ -10888,7 +10890,7 @@
         <v>1.1968085106382842E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>45769</v>
       </c>
@@ -10921,7 +10923,7 @@
         <v>1.8124897017630488E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>45768</v>
       </c>
@@ -10954,7 +10956,7 @@
         <v>7.2083879423329757E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>45764</v>
       </c>
@@ -10987,7 +10989,7 @@
         <v>1.4445981250960551E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
         <v>45763</v>
       </c>
@@ -11020,7 +11022,7 @@
         <v>1.2867647058823609E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>45762</v>
       </c>
@@ -11053,7 +11055,7 @@
         <v>3.0120481927711534E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3">
         <v>45761</v>
       </c>
@@ -11086,7 +11088,7 @@
         <v>6.2864840592725367E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>45758</v>
       </c>
@@ -11119,7 +11121,7 @@
         <v>1.7829347672279658E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="3">
         <v>45757</v>
       </c>
@@ -11152,7 +11154,7 @@
         <v>1.3127853881278614E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>45756</v>
       </c>
@@ -11185,7 +11187,7 @@
         <v>6.4136825227151311E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3">
         <v>45755</v>
       </c>
@@ -11218,7 +11220,7 @@
         <v>7.1890726096334595E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>45754</v>
       </c>
@@ -11251,7 +11253,7 @@
         <v>6.9013112491373126E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="3">
         <v>45751</v>
       </c>
@@ -11284,7 +11286,7 @@
         <v>1.12022925621987E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>45750</v>
       </c>
@@ -11317,7 +11319,7 @@
         <v>6.3091482649843935E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="3">
         <v>45749</v>
       </c>
@@ -11350,7 +11352,7 @@
         <v>3.9830719442369962E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>45748</v>
       </c>
@@ -11383,7 +11385,7 @@
         <v>5.0658561296859205E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
         <v>45747</v>
       </c>
@@ -11416,7 +11418,7 @@
         <v>2.6644059585806271E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>45744</v>
       </c>
@@ -11449,7 +11451,7 @@
         <v>9.8280098280098364E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
         <v>45743</v>
       </c>
@@ -11482,7 +11484,7 @@
         <v>2.5523226135784152E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>45742</v>
       </c>
@@ -11515,7 +11517,7 @@
         <v>3.1063939943049468E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
         <v>45741</v>
       </c>
@@ -11548,7 +11550,7 @@
         <v>4.1046690610569555E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>45740</v>
       </c>
@@ -11581,7 +11583,7 @@
         <v>1.7307202850598131E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="3">
         <v>45737</v>
       </c>
@@ -11614,7 +11616,7 @@
         <v>2.238712111684053E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>45736</v>
       </c>
@@ -11647,7 +11649,7 @@
         <v>2.2753128555176075E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="3">
         <v>45735</v>
       </c>
@@ -11680,7 +11682,7 @@
         <v>6.4186378224177186E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>45734</v>
       </c>
@@ -11713,7 +11715,7 @@
         <v>4.9273220004926272E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
         <v>45733</v>
       </c>
@@ -11746,7 +11748,7 @@
         <v>5.7449731484949893E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>45730</v>
       </c>
@@ -11779,7 +11781,7 @@
         <v>1.463414634146332E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>45729</v>
       </c>
@@ -11812,7 +11814,7 @@
         <v>8.4220956155562788E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>45728</v>
       </c>
@@ -11845,7 +11847,7 @@
         <v>7.1791063250402059E-3</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="3">
         <v>45727</v>
       </c>
@@ -11878,7 +11880,7 @@
         <v>7.3495636196600888E-3</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>45726</v>
       </c>
@@ -11911,7 +11913,7 @@
         <v>8.7180060355427722E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>45723</v>
       </c>
@@ -11944,7 +11946,7 @@
         <v>1.0423748017221903E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>45722</v>
       </c>
@@ -11977,7 +11979,7 @@
         <v>4.9036777583187164E-3</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
         <v>45721</v>
       </c>
@@ -12010,7 +12012,7 @@
         <v>6.7189249720045353E-3</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>45720</v>
       </c>
@@ -12043,7 +12045,7 @@
         <v>1.0454175862469493E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
         <v>45719</v>
       </c>
@@ -12076,7 +12078,7 @@
         <v>5.5308404472765868E-3</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>45716</v>
       </c>
@@ -12109,7 +12111,7 @@
         <v>4.1895784236711218E-3</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
         <v>45715</v>
       </c>
@@ -12142,7 +12144,7 @@
         <v>6.8676077832887424E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>45714</v>
       </c>
@@ -12175,7 +12177,7 @@
         <v>6.5458207452164657E-3</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
         <v>45713</v>
       </c>
@@ -12208,7 +12210,7 @@
         <v>9.4419561796394123E-3</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>45712</v>
       </c>
@@ -12241,7 +12243,7 @@
         <v>4.7636956249216813E-3</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="3">
         <v>45709</v>
       </c>
@@ -12274,7 +12276,7 @@
         <v>2.1565869667135612E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>45708</v>
       </c>
@@ -12307,7 +12309,7 @@
         <v>6.2245630835529543E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>45707</v>
       </c>
@@ -12340,7 +12342,7 @@
         <v>1.1658475254314814E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>45706</v>
       </c>
@@ -12373,7 +12375,7 @@
         <v>3.7383177570092666E-3</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
         <v>45702</v>
       </c>
@@ -12406,7 +12408,7 @@
         <v>1.3156128339374394E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>45701</v>
       </c>
@@ -12439,7 +12441,7 @@
         <v>2.1905805038335176E-3</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="3">
         <v>45700</v>
       </c>
@@ -12472,7 +12474,7 @@
         <v>6.2024245841555683E-3</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>45699</v>
       </c>
@@ -12505,7 +12507,7 @@
         <v>2.8498147620404069E-3</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>45698</v>
       </c>
@@ -12538,7 +12540,7 @@
         <v>5.5208484672381597E-3</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>45695</v>
       </c>
@@ -12571,7 +12573,7 @@
         <v>1.0534236267870489E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>45694</v>
       </c>
@@ -12604,7 +12606,7 @@
         <v>1.7751479289941502E-3</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>45693</v>
       </c>
@@ -12637,7 +12639,7 @@
         <v>5.3619302949062366E-3</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="3">
         <v>45692</v>
       </c>
@@ -12670,7 +12672,7 @@
         <v>6.2111801242236081E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>45691</v>
       </c>
@@ -12703,7 +12705,7 @@
         <v>5.4315027157512954E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>45688</v>
       </c>
@@ -12736,7 +12738,7 @@
         <v>8.1366965012204754E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>45687</v>
       </c>
@@ -12769,7 +12771,7 @@
         <v>1.0096075557726654E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
         <v>45686</v>
       </c>
@@ -12802,7 +12804,7 @@
         <v>5.6621579112929336E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>45685</v>
       </c>
@@ -12843,25 +12845,25 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L255"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="4" width="8.26953125" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="7" width="4.81640625" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="7" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -12896,7 +12898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>46050</v>
       </c>
@@ -12937,7 +12939,7 @@
         <v>1.3401633387002536E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46049</v>
       </c>
@@ -12978,7 +12980,7 @@
         <v>1.4401219771773634E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>46048</v>
       </c>
@@ -13019,7 +13021,7 @@
         <v>1.5128720760029071E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>46045</v>
       </c>
@@ -13060,7 +13062,7 @@
         <v>1.5193035476976199E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>46044</v>
       </c>
@@ -13101,7 +13103,7 @@
         <v>1.5237572709837928E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>46043</v>
       </c>
@@ -13142,7 +13144,7 @@
         <v>1.5143243215992128E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>46042</v>
       </c>
@@ -13183,7 +13185,7 @@
         <v>1.5366107896316898E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>46038</v>
       </c>
@@ -13224,7 +13226,7 @@
         <v>1.4529389617065548E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>46037</v>
       </c>
@@ -13265,7 +13267,7 @@
         <v>1.4391060832457897E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>46036</v>
       </c>
@@ -13306,7 +13308,7 @@
         <v>1.4301551367213379E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>46035</v>
       </c>
@@ -13347,7 +13349,7 @@
         <v>1.4752302799539353E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>46034</v>
       </c>
@@ -13388,7 +13390,7 @@
         <v>1.3810464007984266E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>46031</v>
       </c>
@@ -13429,7 +13431,7 @@
         <v>1.3450700624765281E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>46030</v>
       </c>
@@ -13470,7 +13472,7 @@
         <v>1.2817931638513545E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>46029</v>
       </c>
@@ -13511,7 +13513,7 @@
         <v>1.2518444133937559E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>46028</v>
       </c>
@@ -13552,7 +13554,7 @@
         <v>1.212829509984144E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>46027</v>
       </c>
@@ -13593,7 +13595,7 @@
         <v>1.1622926708575515E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46024</v>
       </c>
@@ -13634,7 +13636,7 @@
         <v>1.1359546117980715E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>46022</v>
       </c>
@@ -13675,7 +13677,7 @@
         <v>1.1008474528986626E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46021</v>
       </c>
@@ -13716,7 +13718,7 @@
         <v>1.0631346675122531E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>46020</v>
       </c>
@@ -13757,7 +13759,7 @@
         <v>9.8224704276398782E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46017</v>
       </c>
@@ -13798,7 +13800,7 @@
         <v>9.2562558530173856E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>46015</v>
       </c>
@@ -13839,7 +13841,7 @@
         <v>8.4436477043899859E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>46014</v>
       </c>
@@ -13880,7 +13882,7 @@
         <v>7.5484055625834219E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>46013</v>
       </c>
@@ -13921,7 +13923,7 @@
         <v>7.9979758152198283E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>46010</v>
       </c>
@@ -13962,7 +13964,7 @@
         <v>8.2304295165377041E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>46009</v>
       </c>
@@ -14003,7 +14005,7 @@
         <v>7.757627799199562E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>46008</v>
       </c>
@@ -14044,7 +14046,7 @@
         <v>7.8080683288672802E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>46007</v>
       </c>
@@ -14085,7 +14087,7 @@
         <v>8.066051494925161E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>46006</v>
       </c>
@@ -14126,7 +14128,7 @@
         <v>8.3830123223704173E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>46003</v>
       </c>
@@ -14167,7 +14169,7 @@
         <v>8.2415769398578066E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>46002</v>
       </c>
@@ -14208,7 +14210,7 @@
         <v>7.3349640471498962E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>46001</v>
       </c>
@@ -14249,7 +14251,7 @@
         <v>7.2401290683822162E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>46000</v>
       </c>
@@ -14290,7 +14292,7 @@
         <v>7.6789225170806425E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>45999</v>
       </c>
@@ -14331,7 +14333,7 @@
         <v>8.4913482123375513E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>45996</v>
       </c>
@@ -14372,7 +14374,7 @@
         <v>9.5573705454694482E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>45995</v>
       </c>
@@ -14413,7 +14415,7 @@
         <v>1.0210522647927192E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>45994</v>
       </c>
@@ -14454,7 +14456,7 @@
         <v>1.0373208296200285E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>45993</v>
       </c>
@@ -14495,7 +14497,7 @@
         <v>1.0756768838106287E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>45992</v>
       </c>
@@ -14536,7 +14538,7 @@
         <v>1.1086523561467256E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>45989</v>
       </c>
@@ -14577,7 +14579,7 @@
         <v>1.103977939914875E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45987</v>
       </c>
@@ -14618,7 +14620,7 @@
         <v>1.049500045014282E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>45986</v>
       </c>
@@ -14659,7 +14661,7 @@
         <v>1.0478151029936603E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>45985</v>
       </c>
@@ -14700,7 +14702,7 @@
         <v>1.0823519003559526E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>45982</v>
       </c>
@@ -14741,7 +14743,7 @@
         <v>1.1480548744116295E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>45981</v>
       </c>
@@ -14782,7 +14784,7 @@
         <v>1.1126183771768803E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>45980</v>
       </c>
@@ -14823,7 +14825,7 @@
         <v>1.0996743831752784E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>45979</v>
       </c>
@@ -14860,7 +14862,7 @@
         <v>1.1124133685932432E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>45978</v>
       </c>
@@ -14901,7 +14903,7 @@
         <v>1.1131183109400727E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>45975</v>
       </c>
@@ -14942,7 +14944,7 @@
         <v>1.091991908518228E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>45974</v>
       </c>
@@ -14983,7 +14985,7 @@
         <v>1.0211719834615007E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>45973</v>
       </c>
@@ -15024,7 +15026,7 @@
         <v>1.0073324218506936E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>45972</v>
       </c>
@@ -15065,7 +15067,7 @@
         <v>9.9912251294404248E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>45971</v>
       </c>
@@ -15106,7 +15108,7 @@
         <v>1.0080449496486291E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>45968</v>
       </c>
@@ -15147,7 +15149,7 @@
         <v>9.9638624459834103E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>45967</v>
       </c>
@@ -15188,7 +15190,7 @@
         <v>9.2391429329724238E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>45966</v>
       </c>
@@ -15229,7 +15231,7 @@
         <v>8.138771748022109E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>45965</v>
       </c>
@@ -15270,7 +15272,7 @@
         <v>7.1599189856612093E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>45964</v>
       </c>
@@ -15311,7 +15313,7 @@
         <v>7.1870607681550885E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>45961</v>
       </c>
@@ -15352,7 +15354,7 @@
         <v>7.3017413786338825E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>45960</v>
       </c>
@@ -15393,7 +15395,7 @@
         <v>6.930595861549798E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>45959</v>
       </c>
@@ -15434,7 +15436,7 @@
         <v>6.9574462930837621E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>45958</v>
       </c>
@@ -15475,7 +15477,7 @@
         <v>7.0574542127489603E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>45957</v>
       </c>
@@ -15516,7 +15518,7 @@
         <v>7.1293468840001144E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>45954</v>
       </c>
@@ -15557,7 +15559,7 @@
         <v>6.9755785773919403E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>45953</v>
       </c>
@@ -15598,7 +15600,7 @@
         <v>6.1392515396005414E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>45952</v>
       </c>
@@ -15639,7 +15641,7 @@
         <v>6.0032604469046442E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>45951</v>
       </c>
@@ -15680,7 +15682,7 @@
         <v>5.702107406852723E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>45950</v>
       </c>
@@ -15721,7 +15723,7 @@
         <v>5.8129959042534408E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>45947</v>
       </c>
@@ -15762,7 +15764,7 @@
         <v>5.1977111441626374E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>45946</v>
       </c>
@@ -15803,7 +15805,7 @@
         <v>5.2822865419037256E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>45945</v>
       </c>
@@ -15844,7 +15846,7 @@
         <v>5.2270031752255927E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>45944</v>
       </c>
@@ -15885,7 +15887,7 @@
         <v>5.2087098373651899E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>45943</v>
       </c>
@@ -15926,7 +15928,7 @@
         <v>5.2703944305737592E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>45940</v>
       </c>
@@ -15967,7 +15969,7 @@
         <v>5.4912294756593533E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>45939</v>
       </c>
@@ -16008,7 +16010,7 @@
         <v>4.9192739671491481E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>45938</v>
       </c>
@@ -16049,7 +16051,7 @@
         <v>4.8588470793635204E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>45937</v>
       </c>
@@ -16090,7 +16092,7 @@
         <v>5.0856828389276871E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>45936</v>
       </c>
@@ -16131,7 +16133,7 @@
         <v>5.0944522097459569E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>45933</v>
       </c>
@@ -16172,7 +16174,7 @@
         <v>5.2091452734318216E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>45932</v>
       </c>
@@ -16213,7 +16215,7 @@
         <v>4.6197602848505586E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>45931</v>
       </c>
@@ -16254,7 +16256,7 @@
         <v>4.6412266859198721E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>45930</v>
       </c>
@@ -16295,7 +16297,7 @@
         <v>4.6481446917214023E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>45929</v>
       </c>
@@ -16336,7 +16338,7 @@
         <v>5.08472569654433E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>45926</v>
       </c>
@@ -16377,7 +16379,7 @@
         <v>5.3272819360153803E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>45925</v>
       </c>
@@ -16418,7 +16420,7 @@
         <v>5.1053864822186504E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>45924</v>
       </c>
@@ -16459,7 +16461,7 @@
         <v>5.2574685849116507E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>45923</v>
       </c>
@@ -16500,7 +16502,7 @@
         <v>5.3650814212789491E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>45922</v>
       </c>
@@ -16541,7 +16543,7 @@
         <v>5.5696586947099058E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>45919</v>
       </c>
@@ -16582,7 +16584,7 @@
         <v>5.5864511098963577E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>45918</v>
       </c>
@@ -16623,7 +16625,7 @@
         <v>5.7992753201486546E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>45917</v>
       </c>
@@ -16664,7 +16666,7 @@
         <v>5.8336590869423905E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>45916</v>
       </c>
@@ -16705,7 +16707,7 @@
         <v>6.0047476653237071E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>45915</v>
       </c>
@@ -16746,7 +16748,7 @@
         <v>6.4014849244286203E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>45912</v>
       </c>
@@ -16787,7 +16789,7 @@
         <v>6.4188279727301649E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>45911</v>
       </c>
@@ -16828,7 +16830,7 @@
         <v>6.1364772097659507E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>45910</v>
       </c>
@@ -16869,7 +16871,7 @@
         <v>6.3781657979608622E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>45909</v>
       </c>
@@ -16910,7 +16912,7 @@
         <v>6.2537915034625597E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>45908</v>
       </c>
@@ -16951,7 +16953,7 @@
         <v>5.9671704810428609E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>45905</v>
       </c>
@@ -16992,7 +16994,7 @@
         <v>6.0453645906023978E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>45904</v>
       </c>
@@ -17033,7 +17035,7 @@
         <v>5.7893465187385017E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>45903</v>
       </c>
@@ -17074,7 +17076,7 @@
         <v>5.9026998834724167E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>45902</v>
       </c>
@@ -17115,7 +17117,7 @@
         <v>5.9599836766147454E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>45898</v>
       </c>
@@ -17156,7 +17158,7 @@
         <v>6.2869099862423545E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>45897</v>
       </c>
@@ -17197,7 +17199,7 @@
         <v>5.9948094742036228E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>45896</v>
       </c>
@@ -17238,7 +17240,7 @@
         <v>5.9568855378731005E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>45895</v>
       </c>
@@ -17279,7 +17281,7 @@
         <v>6.0006470248135726E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>45894</v>
       </c>
@@ -17320,7 +17322,7 @@
         <v>5.9455053598400339E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>45891</v>
       </c>
@@ -17361,7 +17363,7 @@
         <v>6.0791104631275055E-3</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>45890</v>
       </c>
@@ -17402,7 +17404,7 @@
         <v>6.3260152970470735E-3</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>45889</v>
       </c>
@@ -17443,7 +17445,7 @@
         <v>6.5096960182564178E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>45888</v>
       </c>
@@ -17484,7 +17486,7 @@
         <v>6.880643221953823E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>45887</v>
       </c>
@@ -17525,7 +17527,7 @@
         <v>7.1848343939584025E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>45884</v>
       </c>
@@ -17566,7 +17568,7 @@
         <v>8.2856530223610284E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>45883</v>
       </c>
@@ -17607,7 +17609,7 @@
         <v>8.5986951306345569E-3</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>45882</v>
       </c>
@@ -17648,7 +17650,7 @@
         <v>8.7282676031652934E-3</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>45881</v>
       </c>
@@ -17689,7 +17691,7 @@
         <v>9.0678417562060493E-3</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>45880</v>
       </c>
@@ -17730,7 +17732,7 @@
         <v>9.7301465914008175E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>45877</v>
       </c>
@@ -17771,7 +17773,7 @@
         <v>1.0389677052415966E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>45876</v>
       </c>
@@ -17812,7 +17814,7 @@
         <v>1.2077408136883265E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>45875</v>
       </c>
@@ -17853,7 +17855,7 @@
         <v>1.3250159428882928E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>45874</v>
       </c>
@@ -17894,7 +17896,7 @@
         <v>1.4510215621961838E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>45873</v>
       </c>
@@ -17935,7 +17937,7 @@
         <v>1.4649334777038428E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>45870</v>
       </c>
@@ -17976,7 +17978,7 @@
         <v>1.4750521938652825E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>45869</v>
       </c>
@@ -18017,7 +18019,7 @@
         <v>1.5276865655227571E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>45868</v>
       </c>
@@ -18058,7 +18060,7 @@
         <v>1.5668205001619081E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>45867</v>
       </c>
@@ -18099,7 +18101,7 @@
         <v>1.5823228503719693E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>45866</v>
       </c>
@@ -18140,7 +18142,7 @@
         <v>1.6579203441675804E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>45863</v>
       </c>
@@ -18181,7 +18183,7 @@
         <v>1.6979535315554413E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>45862</v>
       </c>
@@ -18222,7 +18224,7 @@
         <v>1.6682190866050873E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>45861</v>
       </c>
@@ -18263,7 +18265,7 @@
         <v>1.6361444270648312E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>45860</v>
       </c>
@@ -18304,7 +18306,7 @@
         <v>1.637472884373635E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>45859</v>
       </c>
@@ -18345,7 +18347,7 @@
         <v>1.602392553177448E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>45856</v>
       </c>
@@ -18386,7 +18388,7 @@
         <v>1.5677600207470728E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>45855</v>
       </c>
@@ -18427,7 +18429,7 @@
         <v>1.4540826471424647E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>45854</v>
       </c>
@@ -18468,7 +18470,7 @@
         <v>1.385389861852389E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>45853</v>
       </c>
@@ -18509,7 +18511,7 @@
         <v>1.3985621837868809E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>45852</v>
       </c>
@@ -18550,7 +18552,7 @@
         <v>1.3706091174936727E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>45849</v>
       </c>
@@ -18591,7 +18593,7 @@
         <v>1.2942721186079757E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>45848</v>
       </c>
@@ -18632,7 +18634,7 @@
         <v>1.2379200789749351E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>45847</v>
       </c>
@@ -18673,7 +18675,7 @@
         <v>1.0910575676418196E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>45846</v>
       </c>
@@ -18714,7 +18716,7 @@
         <v>9.776188713434766E-3</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>45845</v>
       </c>
@@ -18755,7 +18757,7 @@
         <v>8.4574123085465244E-3</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>45841</v>
       </c>
@@ -18796,7 +18798,7 @@
         <v>8.225188392112082E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>45840</v>
       </c>
@@ -18837,7 +18839,7 @@
         <v>7.9646393041132545E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>45839</v>
       </c>
@@ -18878,7 +18880,7 @@
         <v>6.8343468563104347E-3</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>45838</v>
       </c>
@@ -18919,7 +18921,7 @@
         <v>6.9288543360322124E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>45835</v>
       </c>
@@ -18960,7 +18962,7 @@
         <v>6.6762783336777876E-3</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>45834</v>
       </c>
@@ -19001,7 +19003,7 @@
         <v>5.9234771876977756E-3</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>45833</v>
       </c>
@@ -19042,7 +19044,7 @@
         <v>5.4604775140317157E-3</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>45832</v>
       </c>
@@ -19083,7 +19085,7 @@
         <v>5.7701960686735347E-3</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>45831</v>
       </c>
@@ -19124,7 +19126,7 @@
         <v>6.0110296488289743E-3</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>45828</v>
       </c>
@@ -19165,7 +19167,7 @@
         <v>6.7081179624300736E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>45826</v>
       </c>
@@ -19206,7 +19208,7 @@
         <v>6.9123479811866095E-3</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>45825</v>
       </c>
@@ -19247,7 +19249,7 @@
         <v>7.897981640389632E-3</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>45824</v>
       </c>
@@ -19288,7 +19290,7 @@
         <v>8.3983101249448591E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>45821</v>
       </c>
@@ -19329,7 +19331,7 @@
         <v>8.8959309692043485E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>45820</v>
       </c>
@@ -19370,7 +19372,7 @@
         <v>8.8435226976179941E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>45819</v>
       </c>
@@ -19411,7 +19413,7 @@
         <v>9.0368254851370539E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>45818</v>
       </c>
@@ -19452,7 +19454,7 @@
         <v>9.0730935057485411E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>45817</v>
       </c>
@@ -19493,7 +19495,7 @@
         <v>9.9607778591857578E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>45814</v>
       </c>
@@ -19534,7 +19536,7 @@
         <v>1.1004238160454328E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>45813</v>
       </c>
@@ -19575,7 +19577,7 @@
         <v>1.1356313529666031E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>45812</v>
       </c>
@@ -19616,7 +19618,7 @@
         <v>1.1726718946253741E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>45811</v>
       </c>
@@ -19657,7 +19659,7 @@
         <v>1.4145688958764937E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>45810</v>
       </c>
@@ -19698,7 +19700,7 @@
         <v>1.5221008434375436E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>45807</v>
       </c>
@@ -19739,7 +19741,7 @@
         <v>1.5931503527004488E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>45806</v>
       </c>
@@ -19780,7 +19782,7 @@
         <v>1.5540916670252217E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>45805</v>
       </c>
@@ -19821,7 +19823,7 @@
         <v>1.6370963539780965E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>45804</v>
       </c>
@@ -19862,7 +19864,7 @@
         <v>1.7309842863771026E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>45800</v>
       </c>
@@ -19903,7 +19905,7 @@
         <v>1.9204915357975888E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>45799</v>
       </c>
@@ -19944,7 +19946,7 @@
         <v>1.956876987443E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>45798</v>
       </c>
@@ -19985,7 +19987,7 @@
         <v>1.9750479931255688E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>45797</v>
       </c>
@@ -20026,7 +20028,7 @@
         <v>1.9414483612283522E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>45796</v>
       </c>
@@ -20067,7 +20069,7 @@
         <v>1.9222694702100342E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>45793</v>
       </c>
@@ -20108,7 +20110,7 @@
         <v>1.8673740191478178E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
         <v>45792</v>
       </c>
@@ -20149,7 +20151,7 @@
         <v>1.8527257128586761E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>45791</v>
       </c>
@@ -20190,7 +20192,7 @@
         <v>1.8058552406876448E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="3">
         <v>45790</v>
       </c>
@@ -20231,7 +20233,7 @@
         <v>1.7881216533137158E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>45789</v>
       </c>
@@ -20272,7 +20274,7 @@
         <v>1.8308024940342733E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>45786</v>
       </c>
@@ -20313,7 +20315,7 @@
         <v>1.8707337326469359E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>45785</v>
       </c>
@@ -20354,7 +20356,7 @@
         <v>1.7949225603018659E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>45784</v>
       </c>
@@ -20395,7 +20397,7 @@
         <v>1.691764374695949E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>45783</v>
       </c>
@@ -20436,7 +20438,7 @@
         <v>1.6593133452534842E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>45782</v>
       </c>
@@ -20477,7 +20479,7 @@
         <v>1.6521850457678018E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>45779</v>
       </c>
@@ -20518,7 +20520,7 @@
         <v>1.427478963251683E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>45778</v>
       </c>
@@ -20559,7 +20561,7 @@
         <v>1.3274133828297193E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>45777</v>
       </c>
@@ -20600,7 +20602,7 @@
         <v>1.2715898050582616E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>45776</v>
       </c>
@@ -20641,7 +20643,7 @@
         <v>1.2517285477507184E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>45775</v>
       </c>
@@ -20682,7 +20684,7 @@
         <v>1.1859050484624914E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>45772</v>
       </c>
@@ -20723,7 +20725,7 @@
         <v>1.0812675445307604E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>45771</v>
       </c>
@@ -20764,7 +20766,7 @@
         <v>8.9133484263245414E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>45770</v>
       </c>
@@ -20805,7 +20807,7 @@
         <v>8.2948080438026237E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>45769</v>
       </c>
@@ -20838,15 +20840,15 @@
         <v>1.8124897017630488E-2</v>
       </c>
       <c r="K197">
-        <f t="shared" ref="K197:K255" si="10">_xlfn.STDEV.S(E197:E217)</f>
+        <f t="shared" ref="K197:K234" si="10">_xlfn.STDEV.S(E197:E217)</f>
         <v>4.2190610618189588</v>
       </c>
       <c r="L197" s="10">
-        <f t="shared" ref="L197:L255" si="11">AVERAGE(J197:J217)</f>
+        <f t="shared" ref="L197:L234" si="11">AVERAGE(J197:J217)</f>
         <v>8.5490517459081133E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>45768</v>
       </c>
@@ -20887,7 +20889,7 @@
         <v>8.75201479825145E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>45764</v>
       </c>
@@ -20928,7 +20930,7 @@
         <v>8.5171064607840515E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
         <v>45763</v>
       </c>
@@ -20969,7 +20971,7 @@
         <v>8.1348520118058217E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>45762</v>
       </c>
@@ -21010,7 +21012,7 @@
         <v>7.7567412947424415E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="3">
         <v>45761</v>
       </c>
@@ -21051,7 +21053,7 @@
         <v>7.8868805783483386E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>45758</v>
       </c>
@@ -21092,7 +21094,7 @@
         <v>8.2843883060717081E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="3">
         <v>45757</v>
       </c>
@@ -21133,7 +21135,7 @@
         <v>7.8364239224182151E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>45756</v>
       </c>
@@ -21174,7 +21176,7 @@
         <v>7.5531502292640069E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="3">
         <v>45755</v>
       </c>
@@ -21215,7 +21217,7 @@
         <v>7.5977159957851944E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>45754</v>
       </c>
@@ -21256,7 +21258,7 @@
         <v>7.670522349399923E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="3">
         <v>45751</v>
       </c>
@@ -21297,7 +21299,7 @@
         <v>7.8382574335944272E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>45750</v>
       </c>
@@ -21338,7 +21340,7 @@
         <v>7.5383233953144266E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="3">
         <v>45749</v>
       </c>
@@ -21379,7 +21381,7 @@
         <v>7.5578365718391967E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>45748</v>
       </c>
@@ -21420,7 +21422,7 @@
         <v>7.8659843774693157E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
         <v>45747</v>
       </c>
@@ -21461,7 +21463,7 @@
         <v>7.8881264878307763E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>45744</v>
       </c>
@@ -21502,7 +21504,7 @@
         <v>7.9607537480731825E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
         <v>45743</v>
       </c>
@@ -21543,7 +21545,7 @@
         <v>7.819782222134081E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>45742</v>
       </c>
@@ -21584,7 +21586,7 @@
         <v>8.0099487998311295E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
         <v>45741</v>
       </c>
@@ -21625,7 +21627,7 @@
         <v>8.3116422372280108E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>45740</v>
       </c>
@@ -21666,7 +21668,7 @@
         <v>8.3430244545549016E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="3">
         <v>45737</v>
       </c>
@@ -21707,7 +21709,7 @@
         <v>8.5458181124852574E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>45736</v>
       </c>
@@ -21748,7 +21750,7 @@
         <v>7.7761724918525166E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="3">
         <v>45735</v>
       </c>
@@ -21789,7 +21791,7 @@
         <v>8.2229897489380973E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>45734</v>
       </c>
@@ -21830,7 +21832,7 @@
         <v>8.0953554601091247E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
         <v>45733</v>
       </c>
@@ -21871,7 +21873,7 @@
         <v>8.4872033810082567E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>45730</v>
       </c>
@@ -21912,7 +21914,7 @@
         <v>8.3179465884053311E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>45729</v>
       </c>
@@ -21953,7 +21955,7 @@
         <v>7.9164360285335321E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>45728</v>
       </c>
@@ -21994,7 +21996,7 @@
         <v>7.6510893212232527E-3</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="3">
         <v>45727</v>
       </c>
@@ -22035,7 +22037,7 @@
         <v>7.5721246613279173E-3</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>45726</v>
       </c>
@@ -22076,7 +22078,7 @@
         <v>7.7237757398141253E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>45723</v>
       </c>
@@ -22117,7 +22119,7 @@
         <v>7.3931634490260953E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>45722</v>
       </c>
@@ -22158,7 +22160,7 @@
         <v>7.1521245098682034E-3</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
         <v>45721</v>
       </c>
@@ -22199,7 +22201,7 @@
         <v>7.2143865272922478E-3</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>45720</v>
       </c>
@@ -22240,7 +22242,7 @@
         <v>7.1530807055659026E-3</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
         <v>45719</v>
       </c>
@@ -22281,7 +22283,7 @@
         <v>7.0427245455064276E-3</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>45716</v>
       </c>
@@ -22322,7 +22324,7 @@
         <v>7.2601166936230969E-3</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
         <v>45715</v>
       </c>
@@ -22363,7 +22365,7 @@
         <v>7.3302395263669922E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>45714</v>
       </c>
@@ -22397,7 +22399,7 @@
       </c>
       <c r="L235" s="10"/>
     </row>
-    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
         <v>45713</v>
       </c>
@@ -22431,7 +22433,7 @@
       </c>
       <c r="L236" s="10"/>
     </row>
-    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>45712</v>
       </c>
@@ -22465,7 +22467,7 @@
       </c>
       <c r="L237" s="10"/>
     </row>
-    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="3">
         <v>45709</v>
       </c>
@@ -22499,7 +22501,7 @@
       </c>
       <c r="L238" s="10"/>
     </row>
-    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>45708</v>
       </c>
@@ -22533,7 +22535,7 @@
       </c>
       <c r="L239" s="10"/>
     </row>
-    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>45707</v>
       </c>
@@ -22567,7 +22569,7 @@
       </c>
       <c r="L240" s="10"/>
     </row>
-    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>45706</v>
       </c>
@@ -22601,7 +22603,7 @@
       </c>
       <c r="L241" s="10"/>
     </row>
-    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
         <v>45702</v>
       </c>
@@ -22635,7 +22637,7 @@
       </c>
       <c r="L242" s="10"/>
     </row>
-    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>45701</v>
       </c>
@@ -22669,7 +22671,7 @@
       </c>
       <c r="L243" s="10"/>
     </row>
-    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="3">
         <v>45700</v>
       </c>
@@ -22703,7 +22705,7 @@
       </c>
       <c r="L244" s="10"/>
     </row>
-    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>45699</v>
       </c>
@@ -22737,7 +22739,7 @@
       </c>
       <c r="L245" s="10"/>
     </row>
-    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>45698</v>
       </c>
@@ -22771,7 +22773,7 @@
       </c>
       <c r="L246" s="10"/>
     </row>
-    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>45695</v>
       </c>
@@ -22805,7 +22807,7 @@
       </c>
       <c r="L247" s="10"/>
     </row>
-    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>45694</v>
       </c>
@@ -22839,7 +22841,7 @@
       </c>
       <c r="L248" s="10"/>
     </row>
-    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>45693</v>
       </c>
@@ -22873,7 +22875,7 @@
       </c>
       <c r="L249" s="10"/>
     </row>
-    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="3">
         <v>45692</v>
       </c>
@@ -22907,7 +22909,7 @@
       </c>
       <c r="L250" s="10"/>
     </row>
-    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>45691</v>
       </c>
@@ -22941,7 +22943,7 @@
       </c>
       <c r="L251" s="10"/>
     </row>
-    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>45688</v>
       </c>
@@ -22975,7 +22977,7 @@
       </c>
       <c r="L252" s="10"/>
     </row>
-    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>45687</v>
       </c>
@@ -23009,7 +23011,7 @@
       </c>
       <c r="L253" s="10"/>
     </row>
-    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
         <v>45686</v>
       </c>
@@ -23043,7 +23045,7 @@
       </c>
       <c r="L254" s="10"/>
     </row>
-    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>45685</v>
       </c>
